--- a/cuadros/JUNIO/CENTRAL.xlsx
+++ b/cuadros/JUNIO/CENTRAL.xlsx
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor rgb="FF00B0F0"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -550,6 +557,71 @@
       <c r="N2" t="inlineStr">
         <is>
           <t>ID_20260601143246</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PROMAVAL 1008, C.A</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>000104</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NICOLE COLMENARES</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>OTRAS.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Se recibieron </t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>89.64</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>EXCEDENTES</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>ID_20260603101110</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/CENTRAL.xlsx
+++ b/cuadros/JUNIO/CENTRAL.xlsx
@@ -603,7 +603,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Se recibieron </t>
+          <t>Se recibieron 3262,2 kg de cerdo y en factura indican 3245,6 kg, excedente 16,6 kg</t>
         </is>
       </c>
       <c r="J3" s="1" t="n">

--- a/cuadros/JUNIO/CENTRAL.xlsx
+++ b/cuadros/JUNIO/CENTRAL.xlsx
@@ -619,6 +619,11 @@
           <t>EXCEDENTES</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>INC_101704_0.jpg INC_101727_0.jpg</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>ID_20260603101110</t>

--- a/cuadros/JUNIO/CENTRAL.xlsx
+++ b/cuadros/JUNIO/CENTRAL.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>000104</t>
+          <t>0001S04</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NICOLE COLMENARES</t>
+          <t>PROVEEDOR</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">

--- a/cuadros/JUNIO/CENTRAL.xlsx
+++ b/cuadros/JUNIO/CENTRAL.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -57,7 +56,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -420,8 +419,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:M3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -489,11 +488,6 @@
           <t>FOTO_INCIDENCIA</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -554,11 +548,6 @@
           <t>NINGUNA</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>ID_20260601143246</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -622,11 +611,6 @@
       <c r="M3" t="inlineStr">
         <is>
           <t>INC_101704_0.jpg INC_101727_0.jpg</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>ID_20260603101110</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/CENTRAL.xlsx
+++ b/cuadros/JUNIO/CENTRAL.xlsx
@@ -419,8 +419,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6"/>
+  <cols>
+    <col width="33.921875" customWidth="1" min="12" max="12"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -485,6 +488,11 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>FOTO_INCIDENCIA</t>
         </is>
       </c>
@@ -608,7 +616,7 @@
           <t>EXCEDENTES</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>INC_101704_0.jpg INC_101727_0.jpg</t>
         </is>

--- a/cuadros/JUNIO/CENTRAL.xlsx
+++ b/cuadros/JUNIO/CENTRAL.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -25,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
-        <bgColor rgb="FF00B0F0"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -51,12 +46,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -420,10 +414,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6"/>
-  <cols>
-    <col width="33.921875" customWidth="1" min="12" max="12"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -556,6 +547,8 @@
           <t>NINGUNA</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -593,17 +586,13 @@
           <t>OTRAS.</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Se recibieron 3262,2 kg de cerdo y en factura indican 3245,6 kg, excedente 16,6 kg</t>
         </is>
       </c>
-      <c r="J3" s="1" t="n">
+      <c r="J3" t="n">
         <v>89.64</v>
       </c>
       <c r="K3" t="inlineStr">
@@ -616,6 +605,7 @@
           <t>EXCEDENTES</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>INC_101704_0.jpg INC_101727_0.jpg</t>

--- a/cuadros/JUNIO/CENTRAL.xlsx
+++ b/cuadros/JUNIO/CENTRAL.xlsx
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor rgb="FF00B0F0"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -547,8 +554,6 @@
           <t>NINGUNA</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -586,13 +591,12 @@
           <t>OTRAS.</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Se recibieron 3262,2 kg de cerdo y en factura indican 3245,6 kg, excedente 16,6 kg</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="1" t="n">
         <v>89.64</v>
       </c>
       <c r="K3" t="inlineStr">
@@ -605,7 +609,6 @@
           <t>EXCEDENTES</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>INC_101704_0.jpg INC_101727_0.jpg</t>

--- a/cuadros/JUNIO/CENTRAL.xlsx
+++ b/cuadros/JUNIO/CENTRAL.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -612,6 +612,56 @@
       <c r="N3" t="inlineStr">
         <is>
           <t>INC_101704_0.jpg INC_101727_0.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ID_20260608071309</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>INC_071309_0.jpg INC_071309_1.jpg</t>
         </is>
       </c>
     </row>
